--- a/kortdata/PU_personal.xlsx
+++ b/kortdata/PU_personal.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -551,16 +551,6 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Lindring</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Händelsemotstånd</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>Antal exemplar</t>
         </is>
       </c>
@@ -633,14 +623,6 @@
         </is>
       </c>
       <c r="S2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Politikkort</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -714,14 +696,6 @@
       <c r="S3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>Politikkort</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -791,14 +765,6 @@
         </is>
       </c>
       <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>Nämnd</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -872,14 +838,6 @@
         </is>
       </c>
       <c r="S5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>Dialogkort</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -951,14 +909,6 @@
         </is>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>Politikkort</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1030,14 +980,6 @@
         </is>
       </c>
       <c r="S7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>Dialogkort</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1106,9 +1048,7 @@
           <t>Tid &amp; Risk</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1178,14 +1118,6 @@
         </is>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>Dialogkort</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1255,14 +1187,6 @@
         </is>
       </c>
       <c r="S10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>Dialogkort</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1334,14 +1258,6 @@
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>Politikkort</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2156,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2586,12 +2502,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lindring</t>
+          <t>Antal exemplar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lindring</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2600,50 +2516,6 @@
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>Ej tryckt — speldata</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Händelsemotstånd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Händelsemotstand</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nej</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Ej tryckt — kortslag som lindras (Politikkort, Dialogkort, Nämnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Antal exemplar</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nej</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
         <is>
           <t>Antal tryckta kort per spel (exemplar_map: 1)</t>
         </is>
